--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402582</t>
+          <t xml:space="preserve">3404938</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F17">
-        <v>1193</v>
+        <v>750</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402582</t>
+          <t xml:space="preserve">3404938</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F18">
-        <v>442</v>
+        <v>750</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402582</t>
+          <t xml:space="preserve">3418528</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>442</v>
+        <v>1303</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402582</t>
+          <t xml:space="preserve">3419610</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>713</v>
+        <v>366</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402582</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F21">
-        <v>713</v>
+        <v>290</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402728</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F22">
-        <v>709</v>
+        <v>1002</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402728</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F23">
-        <v>711</v>
+        <v>660</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3404938</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F24">
-        <v>750</v>
+        <v>454</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">3404938</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F25">
-        <v>750</v>
+        <v>1009</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3405225</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>268</v>
+        <v>548</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406264</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F27">
-        <v>1750</v>
+        <v>661</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414578</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F28">
-        <v>280</v>
+        <v>1154</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414578</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F29">
-        <v>356</v>
+        <v>807</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414578</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F30">
-        <v>377</v>
+        <v>3631</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414578</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F31">
-        <v>2530</v>
+        <v>1232</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3418528</t>
+          <t xml:space="preserve">3425761</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>1303</v>
+        <v>613</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3419610</t>
+          <t xml:space="preserve">3425761</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F33">
-        <v>366</v>
+        <v>284</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">3425933</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F34">
-        <v>290</v>
+        <v>1436</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">3434129</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F35">
-        <v>1002</v>
+        <v>559</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">3434129</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F36">
-        <v>660</v>
+        <v>340</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,16 +1831,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">378951, 378952, 378953, 378954, 378955</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F37">
-        <v>454</v>
+        <v>3405</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,16 +1881,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">379871</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F38">
-        <v>1009</v>
+        <v>648</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1931,16 +1931,16 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">379871</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F39">
-        <v>548</v>
+        <v>3122</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">379871, 379873</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F40">
-        <v>661</v>
+        <v>8255</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">379911, 379912</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>1154</v>
+        <v>1131</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">5569307</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>807</v>
+        <v>350</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>3631</v>
+        <v>652</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F44">
-        <v>1232</v>
+        <v>332</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425761</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F45">
-        <v>613</v>
+        <v>316</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425761</t>
+          <t xml:space="preserve">5569838</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>284</v>
+        <v>581</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425933</t>
+          <t xml:space="preserve">5570831</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>1436</v>
+        <v>326</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2381,16 +2381,16 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">3434129</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F48">
-        <v>559</v>
+        <v>616</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3434129</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F49">
-        <v>340</v>
+        <v>1062</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">379871</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="F50">
-        <v>3122</v>
+        <v>697</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,16 +2531,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569307</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F51">
-        <v>350</v>
+        <v>673</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2581,16 +2581,16 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="F52">
-        <v>652</v>
+        <v>618</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2631,16 +2631,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F53">
-        <v>332</v>
+        <v>474</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2681,16 +2681,16 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F54">
-        <v>316</v>
+        <v>1383</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2731,16 +2731,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569838</t>
+          <t xml:space="preserve">5574741</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F55">
-        <v>581</v>
+        <v>502</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570831</t>
+          <t xml:space="preserve">748452, 3400636</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F56">
-        <v>326</v>
+        <v>288</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748457, 8467108</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F57">
-        <v>616</v>
+        <v>3453</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2881,16 +2881,16 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748457, 8467108</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="F58">
-        <v>1062</v>
+        <v>253</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,16 +2931,16 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748462, 5569969</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F59">
-        <v>697</v>
+        <v>640</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748469, 5570428</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F60">
-        <v>673</v>
+        <v>375</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3031,16 +3031,16 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748478, 3400670</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F61">
-        <v>618</v>
+        <v>467</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3081,16 +3081,16 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748487, 3412860</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F62">
-        <v>474</v>
+        <v>379</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3131,16 +3131,16 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">748487, 3412860</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F63">
-        <v>1383</v>
+        <v>731</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3181,16 +3181,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5574741</t>
+          <t xml:space="preserve">748529, 3402733</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F64">
-        <v>502</v>
+        <v>1546</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3231,16 +3231,16 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">748452, 3400636</t>
+          <t xml:space="preserve">748529, 3402733</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F65">
-        <v>288</v>
+        <v>976</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3281,16 +3281,16 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">748457, 8467108</t>
+          <t xml:space="preserve">748533, 5572052</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>3453</v>
+        <v>1501</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">748457, 8467108</t>
+          <t xml:space="preserve">748534, 5572974</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F67">
-        <v>253</v>
+        <v>2276</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">748462, 5569969</t>
+          <t xml:space="preserve">748614, 3396685</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="F68">
-        <v>640</v>
+        <v>1878</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3431,16 +3431,16 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">748469, 5570428</t>
+          <t xml:space="preserve">748671, 3396748</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F69">
-        <v>375</v>
+        <v>2575</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">748478, 3400670</t>
+          <t xml:space="preserve">748787, 3402163</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F70">
-        <v>467</v>
+        <v>288</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">748487, 3412860</t>
+          <t xml:space="preserve">748833, 8656363</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="F71">
-        <v>379</v>
+        <v>4005</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3581,16 +3581,16 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">748487, 3412860</t>
+          <t xml:space="preserve">748841, 3432338</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F72">
-        <v>731</v>
+        <v>377</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">748529, 3402733</t>
+          <t xml:space="preserve">7566758</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>1546</v>
+        <v>343</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3681,16 +3681,16 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">748529, 3402733</t>
+          <t xml:space="preserve">7944969</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F74">
-        <v>976</v>
+        <v>505</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">748533, 5572052</t>
+          <t xml:space="preserve">8104619</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="F75">
-        <v>1501</v>
+        <v>311</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3781,16 +3781,16 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">748534, 5572974</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F76">
-        <v>2276</v>
+        <v>881</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3831,16 +3831,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">748555, 3406264</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F77">
-        <v>1635</v>
+        <v>953</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3881,16 +3881,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">748614, 3396685</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F78">
-        <v>1878</v>
+        <v>817</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3931,16 +3931,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">748671, 3396748</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="F79">
-        <v>2575</v>
+        <v>616</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3981,16 +3981,16 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">748686, 3396919</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F80">
-        <v>454</v>
+        <v>1687</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4031,16 +4031,16 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">748787, 3402163</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F81">
-        <v>288</v>
+        <v>804</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4081,16 +4081,16 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">748825, 3432340</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="F82">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4131,16 +4131,16 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">748833, 8656363</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F83">
-        <v>4005</v>
+        <v>1889</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4181,16 +4181,16 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">748841, 3432338</t>
+          <t xml:space="preserve">8125673</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F84">
-        <v>377</v>
+        <v>272</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4231,16 +4231,16 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566758</t>
+          <t xml:space="preserve">8714950</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F85">
-        <v>343</v>
+        <v>965</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4281,16 +4281,16 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7944969</t>
+          <t xml:space="preserve">8715221</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F86">
-        <v>505</v>
+        <v>1143</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4331,16 +4331,16 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8104619</t>
+          <t xml:space="preserve">8835350, 100788332</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F87">
-        <v>311</v>
+        <v>946</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4381,16 +4381,16 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898146</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F88">
-        <v>881</v>
+        <v>525</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4431,16 +4431,16 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F89">
-        <v>953</v>
+        <v>476</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4481,16 +4481,16 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F90">
-        <v>817</v>
+        <v>800</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4531,16 +4531,16 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F91">
-        <v>616</v>
+        <v>418</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4581,16 +4581,16 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F92">
-        <v>1687</v>
+        <v>418</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4631,16 +4631,16 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F93">
-        <v>804</v>
+        <v>418</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4681,16 +4681,16 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F94">
-        <v>259</v>
+        <v>1307</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4731,16 +4731,16 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F95">
-        <v>1889</v>
+        <v>1266</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4781,16 +4781,16 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8125673</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F96">
-        <v>272</v>
+        <v>2508</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4831,16 +4831,16 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8467113</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F97">
-        <v>668</v>
+        <v>1671</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4881,30 +4881,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8467113</t>
+          <t xml:space="preserve">3400717</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F98">
-        <v>395</v>
+        <v>584</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016107</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4931,30 +4931,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8467113</t>
+          <t xml:space="preserve">3421316</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F99">
-        <v>3356</v>
+        <v>615</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016108</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8714950</t>
+          <t xml:space="preserve">3415384</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,21 +4990,21 @@
         </is>
       </c>
       <c r="F100">
-        <v>965</v>
+        <v>939</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017734</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8715221</t>
+          <t xml:space="preserve">3426717</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,21 +5040,21 @@
         </is>
       </c>
       <c r="F101">
-        <v>1143</v>
+        <v>741</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017733</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">8835350, 100788332</t>
+          <t xml:space="preserve">5570155</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,21 +5090,21 @@
         </is>
       </c>
       <c r="F102">
-        <v>946</v>
+        <v>1312</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017736</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5131,30 +5131,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898146</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F103">
-        <v>525</v>
+        <v>1266</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200018138</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -5181,30 +5181,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F104">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019505</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -5231,30 +5231,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="F105">
-        <v>800</v>
+        <v>448</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019505</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5281,30 +5281,30 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="F106">
-        <v>418</v>
+        <v>581</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019505</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -5331,30 +5331,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">5570358</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F107">
-        <v>418</v>
+        <v>658</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020421</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -5381,30 +5381,30 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">7232806</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F108">
-        <v>418</v>
+        <v>877</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020420</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5431,30 +5431,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">7894370</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>1307</v>
+        <v>627</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020414</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5481,30 +5481,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">5569882</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F110">
-        <v>1266</v>
+        <v>765</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200020679</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-09-18</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -5531,30 +5531,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">5571294</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F111">
-        <v>2508</v>
+        <v>766</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200022190</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-10-12</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -5581,30 +5581,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">8125673</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F112">
-        <v>1671</v>
+        <v>524</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200024595</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-11-26</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -5631,25 +5631,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400717</t>
+          <t xml:space="preserve">3405225</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F113">
-        <v>584</v>
+        <v>268</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016107</t>
+          <t xml:space="preserve">200026458</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-26</t>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421316</t>
+          <t xml:space="preserve">3396613</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>615</v>
+        <v>3586</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016108</t>
+          <t xml:space="preserve">200026490</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-26</t>
+          <t xml:space="preserve">2020-01-08</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,25 +5731,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415384</t>
+          <t xml:space="preserve">8467113</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F115">
-        <v>939</v>
+        <v>668</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017734</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-19</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3426717</t>
+          <t xml:space="preserve">8467113</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F116">
-        <v>741</v>
+        <v>395</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017733</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-19</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570155</t>
+          <t xml:space="preserve">8467113</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F117">
-        <v>1312</v>
+        <v>2481</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017736</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-19</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">379871</t>
+          <t xml:space="preserve">8467113</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F118">
-        <v>648</v>
+        <v>3356</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018139</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">379871, 379873</t>
+          <t xml:space="preserve">10035737</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5940,16 +5940,16 @@
         </is>
       </c>
       <c r="F119">
-        <v>8255</v>
+        <v>6718</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018139</t>
+          <t xml:space="preserve">200028327</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">1808851</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F120">
-        <v>1266</v>
+        <v>3504</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018138</t>
+          <t xml:space="preserve">200028325</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">8104619</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>375</v>
+        <v>1176</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019505</t>
+          <t xml:space="preserve">200028326</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">8898146</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F122">
-        <v>448</v>
+        <v>254</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019505</t>
+          <t xml:space="preserve">311232933</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2020-03-03</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">748825, 3432340</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F123">
-        <v>581</v>
+        <v>311</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019505</t>
+          <t xml:space="preserve">200029046</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2020-03-11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570358</t>
+          <t xml:space="preserve">7005544</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>658</v>
+        <v>1109</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020421</t>
+          <t xml:space="preserve">200029246</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2020-03-15</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232806</t>
+          <t xml:space="preserve">3394479</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>877</v>
+        <v>306</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020420</t>
+          <t xml:space="preserve">200034083</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7894370</t>
+          <t xml:space="preserve">3396606</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6290,16 +6290,16 @@
         </is>
       </c>
       <c r="F126">
-        <v>627</v>
+        <v>3016</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020414</t>
+          <t xml:space="preserve">200035511</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2020-08-19</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569882</t>
+          <t xml:space="preserve">3400568</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="F127">
-        <v>765</v>
+        <v>1436</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020679</t>
+          <t xml:space="preserve">200035481</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-18</t>
+          <t xml:space="preserve">2020-08-19</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571294</t>
+          <t xml:space="preserve">8897956</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6390,16 +6390,16 @@
         </is>
       </c>
       <c r="F128">
-        <v>766</v>
+        <v>1332</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022190</t>
+          <t xml:space="preserve">200037994</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-12</t>
+          <t xml:space="preserve">2020-09-28</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8125673</t>
+          <t xml:space="preserve">10167611</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6440,16 +6440,16 @@
         </is>
       </c>
       <c r="F129">
-        <v>524</v>
+        <v>5843</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024595</t>
+          <t xml:space="preserve">200040585</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-26</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3396613</t>
+          <t xml:space="preserve">3402582</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6490,16 +6490,16 @@
         </is>
       </c>
       <c r="F130">
-        <v>3586</v>
+        <v>1193</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026490</t>
+          <t xml:space="preserve">200040575</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-08</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6531,25 +6531,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8467113</t>
+          <t xml:space="preserve">3402582</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F131">
-        <v>2481</v>
+        <v>442</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027989</t>
+          <t xml:space="preserve">200040575</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-12</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6581,25 +6581,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">10035737</t>
+          <t xml:space="preserve">3402582</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F132">
-        <v>6718</v>
+        <v>442</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028327</t>
+          <t xml:space="preserve">200040575</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-22</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6631,25 +6631,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808851</t>
+          <t xml:space="preserve">3402582</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F133">
-        <v>3504</v>
+        <v>713</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028325</t>
+          <t xml:space="preserve">200040575</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-22</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6681,25 +6681,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">379911, 379912</t>
+          <t xml:space="preserve">3402582</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F134">
-        <v>1131</v>
+        <v>713</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028329</t>
+          <t xml:space="preserve">200040575</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-22</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8104619</t>
+          <t xml:space="preserve">7566758</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6740,16 +6740,16 @@
         </is>
       </c>
       <c r="F135">
-        <v>1176</v>
+        <v>3470</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028326</t>
+          <t xml:space="preserve">200040581</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-22</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6781,25 +6781,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898146</t>
+          <t xml:space="preserve">3406979</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F136">
-        <v>254</v>
+        <v>1593</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232933</t>
+          <t xml:space="preserve">200041375</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-03</t>
+          <t xml:space="preserve">2020-11-19</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,25 +6831,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7005544</t>
+          <t xml:space="preserve">3414572</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F137">
-        <v>1109</v>
+        <v>1790</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029246</t>
+          <t xml:space="preserve">200041995</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-15</t>
+          <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6881,25 +6881,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3394479</t>
+          <t xml:space="preserve">3414572</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F138">
-        <v>306</v>
+        <v>1959</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034083</t>
+          <t xml:space="preserve">200041995</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3396606</t>
+          <t xml:space="preserve">3414572</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F139">
-        <v>3016</v>
+        <v>2570</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035511</t>
+          <t xml:space="preserve">200041995</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-19</t>
+          <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400568</t>
+          <t xml:space="preserve">3416937</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>1436</v>
+        <v>6345</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035481</t>
+          <t xml:space="preserve">200042559</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-19</t>
+          <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8897956</t>
+          <t xml:space="preserve">8736395</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F141">
-        <v>1332</v>
+        <v>5503</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037994</t>
+          <t xml:space="preserve">200042869</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-28</t>
+          <t xml:space="preserve">2020-12-13</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10167611</t>
+          <t xml:space="preserve">3406264</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F142">
-        <v>5843</v>
+        <v>1750</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040585</t>
+          <t xml:space="preserve">100198611</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-08</t>
+          <t xml:space="preserve">2020-12-15</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,25 +7131,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566758</t>
+          <t xml:space="preserve">748555, 3406264</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F143">
-        <v>3470</v>
+        <v>1635</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040581</t>
+          <t xml:space="preserve">100198611</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-08</t>
+          <t xml:space="preserve">2020-12-15</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406979</t>
+          <t xml:space="preserve">1802218</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F144">
-        <v>1593</v>
+        <v>1609</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041375</t>
+          <t xml:space="preserve">200043059</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-19</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7231,25 +7231,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414572</t>
+          <t xml:space="preserve">3402728</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F145">
-        <v>1790</v>
+        <v>709</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041995</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-30</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7281,25 +7281,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414572</t>
+          <t xml:space="preserve">3402728</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="F146">
-        <v>1959</v>
+        <v>253</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041995</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-30</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7331,25 +7331,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414572</t>
+          <t xml:space="preserve">3402728</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F147">
-        <v>2570</v>
+        <v>711</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041995</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-30</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3416937</t>
+          <t xml:space="preserve">3404938</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7390,16 +7390,16 @@
         </is>
       </c>
       <c r="F148">
-        <v>6345</v>
+        <v>951</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042559</t>
+          <t xml:space="preserve">200043097</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-08</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7431,25 +7431,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736395</t>
+          <t xml:space="preserve">3406264</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F149">
-        <v>5503</v>
+        <v>777</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042869</t>
+          <t xml:space="preserve">200043087</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-13</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802218</t>
+          <t xml:space="preserve">3433444</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="F150">
-        <v>1609</v>
+        <v>4284</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043059</t>
+          <t xml:space="preserve">200043075</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7531,20 +7531,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402728</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>253</v>
+        <v>1197</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043071</t>
+          <t xml:space="preserve">200043063</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">3404938</t>
+          <t xml:space="preserve">9819885</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7590,11 +7590,11 @@
         </is>
       </c>
       <c r="F152">
-        <v>951</v>
+        <v>885</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043097</t>
+          <t xml:space="preserve">200043064</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7631,20 +7631,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406264</t>
+          <t xml:space="preserve">9819885</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F153">
-        <v>777</v>
+        <v>1610</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043087</t>
+          <t xml:space="preserve">200043064</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3433444</t>
+          <t xml:space="preserve">3424284</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7690,16 +7690,16 @@
         </is>
       </c>
       <c r="F154">
-        <v>4284</v>
+        <v>624</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043075</t>
+          <t xml:space="preserve">200043148</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-16</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7740,16 +7740,16 @@
         </is>
       </c>
       <c r="F155">
-        <v>1197</v>
+        <v>251</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043063</t>
+          <t xml:space="preserve">200045608</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-16</t>
+          <t xml:space="preserve">2021-02-14</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">9819885</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F156">
-        <v>885</v>
+        <v>787</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043064</t>
+          <t xml:space="preserve">200045929</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-16</t>
+          <t xml:space="preserve">2021-02-22</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7831,25 +7831,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">9819885</t>
+          <t xml:space="preserve">3406264</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F157">
-        <v>1610</v>
+        <v>376</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043064</t>
+          <t xml:space="preserve">200046089</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-16</t>
+          <t xml:space="preserve">2021-02-24</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424284</t>
+          <t xml:space="preserve">3425933</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7890,16 +7890,16 @@
         </is>
       </c>
       <c r="F158">
-        <v>624</v>
+        <v>4456</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043148</t>
+          <t xml:space="preserve">200046380</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">7845330</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7940,16 +7940,16 @@
         </is>
       </c>
       <c r="F159">
-        <v>251</v>
+        <v>1199</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045608</t>
+          <t xml:space="preserve">200046374</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-14</t>
+          <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">7845330</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F160">
-        <v>787</v>
+        <v>1959</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045929</t>
+          <t xml:space="preserve">200046374</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-22</t>
+          <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406264</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F161">
-        <v>376</v>
+        <v>1548</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046089</t>
+          <t xml:space="preserve">200050159</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-24</t>
+          <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425933</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F162">
-        <v>4456</v>
+        <v>326</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046380</t>
+          <t xml:space="preserve">200050160</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-03</t>
+          <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,25 +8131,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7845330</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F163">
-        <v>1199</v>
+        <v>4295</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046374</t>
+          <t xml:space="preserve">200050161</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-03</t>
+          <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,25 +8181,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7845330</t>
+          <t xml:space="preserve">3418528</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F164">
-        <v>1959</v>
+        <v>2790</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046374</t>
+          <t xml:space="preserve">310000809</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-03</t>
+          <t xml:space="preserve">2022-06-28</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">3426087</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F165">
-        <v>1548</v>
+        <v>1944</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050159</t>
+          <t xml:space="preserve">310034756</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-14</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,25 +8281,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">3407563</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F166">
-        <v>326</v>
+        <v>3813</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050160</t>
+          <t xml:space="preserve">311015451</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-14</t>
+          <t xml:space="preserve">2023-09-03</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,25 +8331,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">100054071</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F167">
-        <v>4295</v>
+        <v>1112</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050161</t>
+          <t xml:space="preserve">311053110</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-14</t>
+          <t xml:space="preserve">2024-05-08</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3418528</t>
+          <t xml:space="preserve">8125673</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F168">
-        <v>2790</v>
+        <v>380</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000809</t>
+          <t xml:space="preserve">311074174</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-28</t>
+          <t xml:space="preserve">2024-09-18</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3426087</t>
+          <t xml:space="preserve">3407465</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8440,16 +8440,16 @@
         </is>
       </c>
       <c r="F169">
-        <v>1944</v>
+        <v>366</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034756</t>
+          <t xml:space="preserve">311098817</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-12</t>
+          <t xml:space="preserve">2025-03-04</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,25 +8481,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414578</t>
+          <t xml:space="preserve">100071617</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F170">
-        <v>433</v>
+        <v>550</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">310036850</t>
+          <t xml:space="preserve">311155911</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-25</t>
+          <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,35 +8531,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3407563</t>
+          <t xml:space="preserve">7008753</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F171">
-        <v>3813</v>
+        <v>1014</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311015451</t>
+          <t xml:space="preserve">311221399</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-09-03</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8581,35 +8581,35 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054071</t>
+          <t xml:space="preserve">7008753</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F172">
-        <v>1112</v>
+        <v>402</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053110</t>
+          <t xml:space="preserve">311221400</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-08</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8631,35 +8631,35 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">8125673</t>
+          <t xml:space="preserve">7683537</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F173">
-        <v>380</v>
+        <v>857</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311074174</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-18</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8681,35 +8681,35 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3407465</t>
+          <t xml:space="preserve">7683537</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F174">
-        <v>366</v>
+        <v>1434</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098817</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-04</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8731,35 +8731,35 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">100071617</t>
+          <t xml:space="preserve">7683537</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F175">
-        <v>550</v>
+        <v>1042</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155911</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-28</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7008753</t>
+          <t xml:space="preserve">7683537</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F176">
-        <v>1014</v>
+        <v>880</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221399</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7008753</t>
+          <t xml:space="preserve">7683537</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F177">
-        <v>402</v>
+        <v>891</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221400</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F178">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">7683537</t>
+          <t xml:space="preserve">5569460</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F179">
-        <v>1434</v>
+        <v>269</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311236522</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">7683537</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>1042</v>
+        <v>418</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311241555</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7683537</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F181">
-        <v>880</v>
+        <v>424</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311241554</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">7683537</t>
+          <t xml:space="preserve">5569465</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F182">
-        <v>891</v>
+        <v>607</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311244213</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,25 +9131,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">7683537</t>
+          <t xml:space="preserve">3414578</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F183">
-        <v>857</v>
+        <v>433</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311244324</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,25 +9181,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569460</t>
+          <t xml:space="preserve">3414578</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F184">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236522</t>
+          <t xml:space="preserve">311244324</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9231,25 +9231,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3414578</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F185">
-        <v>418</v>
+        <v>356</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241555</t>
+          <t xml:space="preserve">311244324</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9281,25 +9281,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3414578</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F186">
-        <v>424</v>
+        <v>377</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241554</t>
+          <t xml:space="preserve">311244324</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569465</t>
+          <t xml:space="preserve">3414578</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F187">
-        <v>607</v>
+        <v>2530</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244213</t>
+          <t xml:space="preserve">311244324</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10581,25 +10581,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">378951, 378952, 378953, 378954, 378955</t>
+          <t xml:space="preserve">748686, 3396919</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F212">
-        <v>3405</v>
+        <v>454</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361096</t>
+          <t xml:space="preserve">311428321</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-22</t>
+          <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">

--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -91,17 +91,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Alle 12</t>
+          <t xml:space="preserve">Bjerget 12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100040700</t>
+          <t xml:space="preserve">748478, 3400670</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>631</v>
+        <v>467</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,26 +151,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglgårdsvej 7</t>
+          <t xml:space="preserve">Dragskilde 4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7770</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043112</t>
+          <t xml:space="preserve">8104619</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H3">
-        <v>590</v>
+        <v>311</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,26 +211,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvej 85</t>
+          <t xml:space="preserve">Fjordlystvej 4A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043708</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H4">
-        <v>555</v>
+        <v>616</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,26 +271,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 4</t>
+          <t xml:space="preserve">Fjordlystvej 4B</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10016087</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="H5">
-        <v>331</v>
+        <v>697</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,26 +331,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 5</t>
+          <t xml:space="preserve">Fjordlystvej 4C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802259</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H6">
-        <v>1860</v>
+        <v>673</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 5</t>
+          <t xml:space="preserve">Fjordlystvej 4D</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802259</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="H7">
-        <v>762</v>
+        <v>618</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 5</t>
+          <t xml:space="preserve">Fjordlystvej 6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1808851</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="H8">
-        <v>283</v>
+        <v>1383</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Feggesundvej 33</t>
+          <t xml:space="preserve">Fredensvej 9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7742</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3394479</t>
+          <t xml:space="preserve">3425933</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="H9">
-        <v>513</v>
+        <v>1436</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,26 +571,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Feggesundvej 33</t>
+          <t xml:space="preserve">Frederiksgade 5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7742</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3394479</t>
+          <t xml:space="preserve">5569838</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H10">
-        <v>384</v>
+        <v>581</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,26 +631,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Feggesundvej 33</t>
+          <t xml:space="preserve">Fyrvej 104</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7742</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3394479</t>
+          <t xml:space="preserve">748614, 3396685</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H11">
-        <v>454</v>
+        <v>1878</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Feggesundvej 33</t>
+          <t xml:space="preserve">Fyrvej 106</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">7742</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3394479</t>
+          <t xml:space="preserve">748671, 3396748</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H12">
-        <v>700</v>
+        <v>2575</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,26 +751,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyvej 25</t>
+          <t xml:space="preserve">Fyrvej 85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400568</t>
+          <t xml:space="preserve">100043708</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H13">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,26 +811,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyvej 25</t>
+          <t xml:space="preserve">Gl. Feggesundvej 33</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7742</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400568</t>
+          <t xml:space="preserve">3394479</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H14">
-        <v>258</v>
+        <v>513</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 10</t>
+          <t xml:space="preserve">Gl. Feggesundvej 33</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7742</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401915, 100788338</t>
+          <t xml:space="preserve">3394479</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H15">
-        <v>1207</v>
+        <v>384</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 10</t>
+          <t xml:space="preserve">Gl. Feggesundvej 33</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7742</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3401916, 100788339</t>
+          <t xml:space="preserve">3394479</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H16">
-        <v>1030</v>
+        <v>454</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,26 +991,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krovej 3</t>
+          <t xml:space="preserve">Gl. Feggesundvej 33</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7742</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3404938</t>
+          <t xml:space="preserve">3394479</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H17">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krovej 3</t>
+          <t xml:space="preserve">Grønningen 12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3404938</t>
+          <t xml:space="preserve">8898146</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H18">
-        <v>750</v>
+        <v>525</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 43</t>
+          <t xml:space="preserve">Grønningen 12A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3418528</t>
+          <t xml:space="preserve">8125673</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H19">
-        <v>1303</v>
+        <v>272</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sportsvej 3</t>
+          <t xml:space="preserve">Havnen 15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3419610</t>
+          <t xml:space="preserve">5570831</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H20">
-        <v>366</v>
+        <v>326</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Havnevej 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7770</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">748841, 3432338</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H21">
-        <v>290</v>
+        <v>377</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,26 +1291,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Hjul Torv 5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">5569307</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H22">
-        <v>1002</v>
+        <v>350</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,26 +1351,26 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Hjørnet 2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">748457, 8467108</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H23">
-        <v>660</v>
+        <v>3453</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,26 +1411,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Hjørnet 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">748457, 8467108</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H24">
-        <v>454</v>
+        <v>253</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1486,11 +1486,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H25">
-        <v>1009</v>
+        <v>290</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1546,11 +1546,11 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H26">
-        <v>548</v>
+        <v>1002</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H27">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,26 +1651,26 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 11</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H28">
-        <v>1154</v>
+        <v>454</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,26 +1711,26 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 11</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H29">
-        <v>807</v>
+        <v>1009</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,26 +1771,26 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 11</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H30">
-        <v>3631</v>
+        <v>548</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 11</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425576</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H31">
-        <v>1232</v>
+        <v>661</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1B</t>
+          <t xml:space="preserve">Idrætsvej 11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425761</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="H32">
-        <v>613</v>
+        <v>1154</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idrætsvej 1B</t>
+          <t xml:space="preserve">Idrætsvej 11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425761</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="H33">
-        <v>284</v>
+        <v>807</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 9</t>
+          <t xml:space="preserve">Idrætsvej 11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425933</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="H34">
-        <v>1436</v>
+        <v>3631</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Fjordstræde 11</t>
+          <t xml:space="preserve">Idrætsvej 11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3434129</t>
+          <t xml:space="preserve">3425576</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H35">
-        <v>559</v>
+        <v>1232</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Fjordstræde 3A</t>
+          <t xml:space="preserve">Idrætsvej 1B</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3434129</t>
+          <t xml:space="preserve">3425761</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>340</v>
+        <v>613</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,26 +2191,26 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Håndværker Torv 1</t>
+          <t xml:space="preserve">Idrætsvej 1B</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">378951, 378952, 378953, 378954, 378955</t>
+          <t xml:space="preserve">3425761</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H37">
-        <v>3405</v>
+        <v>284</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,26 +2251,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpyttervej 50</t>
+          <t xml:space="preserve">Idrætsvej 5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">379871</t>
+          <t xml:space="preserve">1802259</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H38">
-        <v>648</v>
+        <v>1860</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,26 +2311,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpyttervej 50</t>
+          <t xml:space="preserve">Idrætsvej 5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">379871</t>
+          <t xml:space="preserve">1802259</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H39">
-        <v>3122</v>
+        <v>762</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,17 +2371,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpyttervej 50</t>
+          <t xml:space="preserve">Industrivej 13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">379871, 379873</t>
+          <t xml:space="preserve">748833, 8656363</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="H40">
-        <v>8255</v>
+        <v>4005</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drengshøj 7</t>
+          <t xml:space="preserve">Industrivej 5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,16 +2441,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">379911, 379912</t>
+          <t xml:space="preserve">1808851</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H41">
-        <v>1131</v>
+        <v>283</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2491,17 +2491,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjul Torv 5</t>
+          <t xml:space="preserve">Jernbanegade 4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569307</t>
+          <t xml:space="preserve">10016087</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="H42">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 18</t>
+          <t xml:space="preserve">Kastanievej 47</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2561,16 +2561,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">748534, 5572974</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>652</v>
+        <v>2276</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 18</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,16 +2621,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H44">
-        <v>332</v>
+        <v>881</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 18A</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,16 +2681,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H45">
-        <v>316</v>
+        <v>953</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederiksgade 5</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2741,16 +2741,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569838</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H46">
-        <v>581</v>
+        <v>817</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnen 15</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,16 +2801,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570831</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="H47">
-        <v>326</v>
+        <v>616</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordlystvej 4A</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2861,16 +2861,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="H48">
-        <v>616</v>
+        <v>1687</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platanvej 16</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="H49">
-        <v>1062</v>
+        <v>804</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordlystvej 4B</t>
+          <t xml:space="preserve">Kastanievej 80</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,16 +2981,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">28</t>
         </is>
       </c>
       <c r="H50">
-        <v>697</v>
+        <v>259</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordlystvej 4C</t>
+          <t xml:space="preserve">Kastanievej 80B</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,16 +3041,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H51">
-        <v>673</v>
+        <v>1889</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordlystvej 4D</t>
+          <t xml:space="preserve">Kirkebyvej 25</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,16 +3101,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">3400568</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H52">
-        <v>618</v>
+        <v>634</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Platanvej 14</t>
+          <t xml:space="preserve">Kirkebyvej 25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3161,16 +3161,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">3400568</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H53">
-        <v>474</v>
+        <v>258</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordlystvej 6</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571882</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H54">
-        <v>1383</v>
+        <v>476</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 6</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3281,16 +3281,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5574741</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H55">
-        <v>502</v>
+        <v>800</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 39</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3341,16 +3341,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">748452, 3400636</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H56">
-        <v>288</v>
+        <v>418</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørnet 2</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3401,16 +3401,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">748457, 8467108</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H57">
-        <v>3453</v>
+        <v>418</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjørnet 2</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">748457, 8467108</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H58">
-        <v>253</v>
+        <v>418</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Winthersmøllevej 8</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3521,16 +3521,16 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">748462, 5569969</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H59">
-        <v>640</v>
+        <v>1307</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vegendalvej 15</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,16 +3581,16 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">748469, 5570428</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H60">
-        <v>375</v>
+        <v>1266</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerget 12</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3641,16 +3641,16 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">748478, 3400670</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H61">
-        <v>467</v>
+        <v>2508</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3691,26 +3691,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møgelvej 66</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">748487, 3412860</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H62">
-        <v>379</v>
+        <v>1671</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3751,26 +3751,26 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møgelvej 66</t>
+          <t xml:space="preserve">Krovej 3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">748487, 3412860</t>
+          <t xml:space="preserve">3404938</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H63">
-        <v>731</v>
+        <v>750</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 128</t>
+          <t xml:space="preserve">Krovej 3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,16 +3821,16 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">748529, 3402733</t>
+          <t xml:space="preserve">3404938</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H64">
-        <v>1546</v>
+        <v>750</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 128</t>
+          <t xml:space="preserve">Lerpyttervej 37</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3881,16 +3881,16 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">748529, 3402733</t>
+          <t xml:space="preserve">748533, 5572052</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H65">
-        <v>976</v>
+        <v>1501</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpyttervej 37</t>
+          <t xml:space="preserve">Lerpyttervej 50</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,16 +3941,16 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">748533, 5572052</t>
+          <t xml:space="preserve">379871</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H66">
-        <v>1501</v>
+        <v>3122</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 47</t>
+          <t xml:space="preserve">Lille Fjordstræde 11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">748534, 5572974</t>
+          <t xml:space="preserve">3434129</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="H67">
-        <v>2276</v>
+        <v>559</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4051,26 +4051,26 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvej 104</t>
+          <t xml:space="preserve">Lille Fjordstræde 3A</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">748614, 3396685</t>
+          <t xml:space="preserve">3434129</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H68">
-        <v>1878</v>
+        <v>340</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4111,26 +4111,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvej 106</t>
+          <t xml:space="preserve">Limfjordsgade 9</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">748671, 3396748</t>
+          <t xml:space="preserve">7566758</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H69">
-        <v>2575</v>
+        <v>343</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4171,26 +4171,26 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 9</t>
+          <t xml:space="preserve">Linnetsgade 1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7755</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">748787, 3402163</t>
+          <t xml:space="preserve">8714950</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H70">
-        <v>288</v>
+        <v>965</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4231,26 +4231,26 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 13</t>
+          <t xml:space="preserve">Lufthavnsvej 10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">748833, 8656363</t>
+          <t xml:space="preserve">3401915, 100788338</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H71">
-        <v>4005</v>
+        <v>1207</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4291,17 +4291,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 3</t>
+          <t xml:space="preserve">Lufthavnsvej 10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7770</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">748841, 3432338</t>
+          <t xml:space="preserve">3401916, 100788339</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="H72">
-        <v>377</v>
+        <v>1030</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4351,26 +4351,26 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Limfjordsgade 9</t>
+          <t xml:space="preserve">Lufthavnsvej 10A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566758</t>
+          <t xml:space="preserve">8835350, 100788332</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H73">
-        <v>343</v>
+        <v>946</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4411,26 +4411,26 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævebakken 7</t>
+          <t xml:space="preserve">Lufthavnsvej 9</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7944969</t>
+          <t xml:space="preserve">748787, 3402163</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H74">
-        <v>505</v>
+        <v>288</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4471,26 +4471,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragskilde 4</t>
+          <t xml:space="preserve">Møgelvej 66</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8104619</t>
+          <t xml:space="preserve">748487, 3412860</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4531,26 +4531,26 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Møgelvej 66</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">748487, 3412860</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H76">
-        <v>881</v>
+        <v>731</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Plantagevej 18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4601,16 +4601,16 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H77">
-        <v>953</v>
+        <v>652</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Plantagevej 18</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,16 +4661,16 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H78">
-        <v>817</v>
+        <v>332</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Plantagevej 18A</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,16 +4721,16 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H79">
-        <v>616</v>
+        <v>316</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Platanvej 14</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4781,16 +4781,16 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H80">
-        <v>1687</v>
+        <v>474</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Platanvej 16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">5571882</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="H81">
-        <v>804</v>
+        <v>1062</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4891,26 +4891,26 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80</t>
+          <t xml:space="preserve">Rævebakken 7</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">7944969</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">28</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H82">
-        <v>259</v>
+        <v>505</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 80B</t>
+          <t xml:space="preserve">Sennelsvej 128</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4961,16 +4961,16 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">748529, 3402733</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H83">
-        <v>1889</v>
+        <v>1546</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 12A</t>
+          <t xml:space="preserve">Sennelsvej 128</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5021,16 +5021,16 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8125673</t>
+          <t xml:space="preserve">748529, 3402733</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H84">
-        <v>272</v>
+        <v>976</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5071,17 +5071,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Linnetsgade 1</t>
+          <t xml:space="preserve">Skårhøjvej 15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8714950</t>
+          <t xml:space="preserve">8715221</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="H85">
-        <v>965</v>
+        <v>1143</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skårhøjvej 15</t>
+          <t xml:space="preserve">Solsikkevej 43</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8715221</t>
+          <t xml:space="preserve">3418528</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="H86">
-        <v>1143</v>
+        <v>1303</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 10A</t>
+          <t xml:space="preserve">Sportsvej 3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8835350, 100788332</t>
+          <t xml:space="preserve">3419610</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="H87">
-        <v>946</v>
+        <v>366</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 12</t>
+          <t xml:space="preserve">Stationsvej 39</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5261,16 +5261,16 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898146</t>
+          <t xml:space="preserve">748452, 3400636</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H88">
-        <v>525</v>
+        <v>288</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5311,26 +5311,26 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Teglgårdsvej 7</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7770</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">100043112</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>476</v>
+        <v>590</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Tigervej 6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5381,16 +5381,16 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">5574741</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H90">
-        <v>800</v>
+        <v>502</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Vegendalvej 15</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">748469, 5570428</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="H91">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Winthersmøllevej 8</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">748462, 5569969</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="H92">
-        <v>418</v>
+        <v>640</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5551,26 +5551,26 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Øster Alle 12</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">100040700</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H93">
-        <v>418</v>
+        <v>631</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Bykernen 6</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5621,30 +5621,30 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3400717</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H94">
-        <v>1307</v>
+        <v>584</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016107</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5671,40 +5671,40 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Øster Alle 15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3421316</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H95">
-        <v>1266</v>
+        <v>615</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200016108</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Mellemvej 18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5741,30 +5741,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3415384</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H96">
-        <v>2508</v>
+        <v>939</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017734</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5791,40 +5791,40 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Søndergade 1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3426717</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H97">
-        <v>1671</v>
+        <v>741</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200017733</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bykernen 6</t>
+          <t xml:space="preserve">Tingstrupvej 19</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400717</t>
+          <t xml:space="preserve">5570155</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="H98">
-        <v>584</v>
+        <v>1312</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016107</t>
+          <t xml:space="preserve">200017736</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-26</t>
+          <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,35 +5911,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Øster Alle 15</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421316</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H99">
-        <v>615</v>
+        <v>1266</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">200016108</t>
+          <t xml:space="preserve">200018138</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-26</t>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemvej 18</t>
+          <t xml:space="preserve">Lerpyttervej 50</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415384</t>
+          <t xml:space="preserve">379871</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H100">
-        <v>939</v>
+        <v>648</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017734</t>
+          <t xml:space="preserve">200018139</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-19</t>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 1</t>
+          <t xml:space="preserve">Lerpyttervej 50</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3426717</t>
+          <t xml:space="preserve">379871, 379873</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6050,16 +6050,16 @@
         </is>
       </c>
       <c r="H101">
-        <v>741</v>
+        <v>8255</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017733</t>
+          <t xml:space="preserve">200018139</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-19</t>
+          <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstrupvej 19</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570155</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>1312</v>
+        <v>375</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017736</t>
+          <t xml:space="preserve">200019505</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-19</t>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,35 +6151,35 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Hovedgaden 5</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">3421297</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="H103">
-        <v>1266</v>
+        <v>448</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200018138</t>
+          <t xml:space="preserve">200019505</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-07-31</t>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6226,11 +6226,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="H104">
-        <v>375</v>
+        <v>581</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6271,35 +6271,35 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Kronborgvej 14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">5570358</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H105">
-        <v>448</v>
+        <v>658</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019505</t>
+          <t xml:space="preserve">200020421</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6331,35 +6331,35 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 5</t>
+          <t xml:space="preserve">Munkevej 9E</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3421297</t>
+          <t xml:space="preserve">7232806</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>581</v>
+        <v>877</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019505</t>
+          <t xml:space="preserve">200020420</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 14</t>
+          <t xml:space="preserve">Præstegårdsvej 2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570358</t>
+          <t xml:space="preserve">7894370</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6410,11 +6410,11 @@
         </is>
       </c>
       <c r="H107">
-        <v>658</v>
+        <v>627</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020421</t>
+          <t xml:space="preserve">200020414</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Munkevej 9E</t>
+          <t xml:space="preserve">Kr. Kolds Gade 3</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7232806</t>
+          <t xml:space="preserve">5569882</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6470,16 +6470,16 @@
         </is>
       </c>
       <c r="H108">
-        <v>877</v>
+        <v>765</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020420</t>
+          <t xml:space="preserve">200020679</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-18</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 2</t>
+          <t xml:space="preserve">Ringvej 34</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7894370</t>
+          <t xml:space="preserve">5571294</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,16 +6530,16 @@
         </is>
       </c>
       <c r="H109">
-        <v>627</v>
+        <v>766</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020414</t>
+          <t xml:space="preserve">200022190</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-10-12</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kr. Kolds Gade 3</t>
+          <t xml:space="preserve">Grønningen 12A</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569882</t>
+          <t xml:space="preserve">8125673</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,16 +6590,16 @@
         </is>
       </c>
       <c r="H110">
-        <v>765</v>
+        <v>524</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020679</t>
+          <t xml:space="preserve">200024595</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-18</t>
+          <t xml:space="preserve">2019-11-26</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringvej 34</t>
+          <t xml:space="preserve">Toftholmvej 15</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,25 +6641,25 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5571294</t>
+          <t xml:space="preserve">3405225</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>766</v>
+        <v>268</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022190</t>
+          <t xml:space="preserve">200026458</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-12</t>
+          <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 12A</t>
+          <t xml:space="preserve">Bådsgårdsvej 12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8125673</t>
+          <t xml:space="preserve">3396613</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6710,16 +6710,16 @@
         </is>
       </c>
       <c r="H112">
-        <v>524</v>
+        <v>3586</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">200024595</t>
+          <t xml:space="preserve">200026490</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-11-26</t>
+          <t xml:space="preserve">2020-01-08</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftholmvej 15</t>
+          <t xml:space="preserve">Ebbesvej 3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6761,25 +6761,25 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3405225</t>
+          <t xml:space="preserve">8467113</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H113">
-        <v>268</v>
+        <v>668</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026458</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-07</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,35 +6811,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bådsgårdsvej 12</t>
+          <t xml:space="preserve">Ebbesvej 3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3396613</t>
+          <t xml:space="preserve">8467113</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H114">
-        <v>3586</v>
+        <v>395</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200026490</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-08</t>
+          <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6886,15 +6886,15 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H115">
-        <v>668</v>
+        <v>2481</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027988</t>
+          <t xml:space="preserve">200027989</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6946,11 +6946,11 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H116">
-        <v>395</v>
+        <v>3356</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebbesvej 3</t>
+          <t xml:space="preserve">Asylgade 30</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7001,25 +7001,25 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8467113</t>
+          <t xml:space="preserve">10035737</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H117">
-        <v>2481</v>
+        <v>6718</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027988</t>
+          <t xml:space="preserve">200028327</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-12</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebbesvej 3</t>
+          <t xml:space="preserve">Dragskilde 2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7061,25 +7061,25 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8467113</t>
+          <t xml:space="preserve">8104619</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H118">
-        <v>3356</v>
+        <v>1176</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027988</t>
+          <t xml:space="preserve">200028326</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-12</t>
+          <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 30</t>
+          <t xml:space="preserve">Drengshøj 7</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">10035737</t>
+          <t xml:space="preserve">379911, 379912</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -7130,11 +7130,11 @@
         </is>
       </c>
       <c r="H119">
-        <v>6718</v>
+        <v>1131</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028327</t>
+          <t xml:space="preserve">200028329</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragskilde 2</t>
+          <t xml:space="preserve">Nørrealle 30</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8104619</t>
+          <t xml:space="preserve">8898146</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7250,16 +7250,16 @@
         </is>
       </c>
       <c r="H121">
-        <v>1176</v>
+        <v>254</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028326</t>
+          <t xml:space="preserve">311232933</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-22</t>
+          <t xml:space="preserve">2020-03-03</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrealle 30</t>
+          <t xml:space="preserve">Havnevej 4D</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7770</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898146</t>
+          <t xml:space="preserve">748825, 3432340</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H122">
-        <v>254</v>
+        <v>311</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311232933</t>
+          <t xml:space="preserve">200029046</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-03</t>
+          <t xml:space="preserve">2020-03-11</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,35 +7351,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 4D</t>
+          <t xml:space="preserve">Højtoftevej 50</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7770</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">748825, 3432340</t>
+          <t xml:space="preserve">7005544</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H123">
-        <v>311</v>
+        <v>1109</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029046</t>
+          <t xml:space="preserve">200029246</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-11</t>
+          <t xml:space="preserve">2020-03-15</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,17 +7411,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højtoftevej 50</t>
+          <t xml:space="preserve">Gl. Feggesundvej 31</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7742</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7005544</t>
+          <t xml:space="preserve">3394479</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -7430,16 +7430,16 @@
         </is>
       </c>
       <c r="H124">
-        <v>1109</v>
+        <v>306</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029246</t>
+          <t xml:space="preserve">200034083</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-15</t>
+          <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Feggesundvej 31</t>
+          <t xml:space="preserve">Fyrglimt 2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7742</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3394479</t>
+          <t xml:space="preserve">3396606</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>306</v>
+        <v>3016</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200034083</t>
+          <t xml:space="preserve">200035511</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-07-15</t>
+          <t xml:space="preserve">2020-08-19</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,17 +7531,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrglimt 2</t>
+          <t xml:space="preserve">Kirkebyvej 25</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3396606</t>
+          <t xml:space="preserve">3400568</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7550,11 +7550,11 @@
         </is>
       </c>
       <c r="H126">
-        <v>3016</v>
+        <v>1436</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035511</t>
+          <t xml:space="preserve">200035481</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkebyvej 25</t>
+          <t xml:space="preserve">Langebeksvej 6</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400568</t>
+          <t xml:space="preserve">8897956</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7610,16 +7610,16 @@
         </is>
       </c>
       <c r="H127">
-        <v>1436</v>
+        <v>1332</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035481</t>
+          <t xml:space="preserve">200037994</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-19</t>
+          <t xml:space="preserve">2020-09-28</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebeksvej 6</t>
+          <t xml:space="preserve">Kastanievej 4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8897956</t>
+          <t xml:space="preserve">7566758</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>1332</v>
+        <v>3470</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">200037994</t>
+          <t xml:space="preserve">200040581</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-09-28</t>
+          <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibedalvej 1</t>
+          <t xml:space="preserve">Sennelsvej 65</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">10167611</t>
+          <t xml:space="preserve">3402582</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,11 +7730,11 @@
         </is>
       </c>
       <c r="H129">
-        <v>5843</v>
+        <v>1193</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040585</t>
+          <t xml:space="preserve">200040575</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 65</t>
+          <t xml:space="preserve">Sennelsvej 65A</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7786,11 +7786,11 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H130">
-        <v>1193</v>
+        <v>442</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 65A</t>
+          <t xml:space="preserve">Sennelsvej 65B</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H131">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 65B</t>
+          <t xml:space="preserve">Sennelsvej 65C</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7906,11 +7906,11 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H132">
-        <v>442</v>
+        <v>713</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 65C</t>
+          <t xml:space="preserve">Sennelsvej 65D</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H133">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 65D</t>
+          <t xml:space="preserve">Vibedalvej 1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,20 +8021,20 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402582</t>
+          <t xml:space="preserve">10167611</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H134">
-        <v>713</v>
+        <v>5843</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040575</t>
+          <t xml:space="preserve">200040585</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 4</t>
+          <t xml:space="preserve">Vorupørvej 166</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">7566758</t>
+          <t xml:space="preserve">3406979</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H135">
-        <v>3470</v>
+        <v>1593</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040581</t>
+          <t xml:space="preserve">200041375</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-08</t>
+          <t xml:space="preserve">2020-11-19</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorupørvej 166</t>
+          <t xml:space="preserve">Simons Bakke 37</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8141,25 +8141,25 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406979</t>
+          <t xml:space="preserve">3414572</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H136">
-        <v>1593</v>
+        <v>1790</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041375</t>
+          <t xml:space="preserve">200041995</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-19</t>
+          <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H137">
-        <v>1790</v>
+        <v>1959</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -8266,11 +8266,11 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H138">
-        <v>1959</v>
+        <v>2570</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -8311,35 +8311,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Simons Bakke 37</t>
+          <t xml:space="preserve">Skolegade 1</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7755</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414572</t>
+          <t xml:space="preserve">3416937</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H139">
-        <v>2570</v>
+        <v>6345</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041995</t>
+          <t xml:space="preserve">200042559</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-30</t>
+          <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,35 +8371,35 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 1</t>
+          <t xml:space="preserve">Nørrealle 53</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve">7755</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3416937</t>
+          <t xml:space="preserve">8736395</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H140">
-        <v>6345</v>
+        <v>5503</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042559</t>
+          <t xml:space="preserve">200042869</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-08</t>
+          <t xml:space="preserve">2020-12-13</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrealle 53</t>
+          <t xml:space="preserve">Vesterbyvej 1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,25 +8441,25 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736395</t>
+          <t xml:space="preserve">3406264</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H141">
-        <v>5503</v>
+        <v>1750</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042869</t>
+          <t xml:space="preserve">100198611</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-13</t>
+          <t xml:space="preserve">2020-12-15</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbyvej 1</t>
+          <t xml:space="preserve">Østerild Byvej 7</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,16 +8501,16 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406264</t>
+          <t xml:space="preserve">748555, 3406264</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H142">
-        <v>1750</v>
+        <v>1635</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerild Byvej 7</t>
+          <t xml:space="preserve">Krovej 3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,25 +8561,25 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">748555, 3406264</t>
+          <t xml:space="preserve">3404938</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>1635</v>
+        <v>951</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">100198611</t>
+          <t xml:space="preserve">200043097</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-15</t>
+          <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solsikkevej 2A</t>
+          <t xml:space="preserve">Plantagevej 18</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802218</t>
+          <t xml:space="preserve">5569798</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8630,11 +8630,11 @@
         </is>
       </c>
       <c r="H144">
-        <v>1609</v>
+        <v>1197</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043059</t>
+          <t xml:space="preserve">200043063</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8671,30 +8671,30 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennelsvej 122</t>
+          <t xml:space="preserve">Prins Burisvej 2</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7770</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402728</t>
+          <t xml:space="preserve">3433444</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H145">
-        <v>709</v>
+        <v>4284</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043075</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8806,11 +8806,11 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H147">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krovej 3</t>
+          <t xml:space="preserve">Sennelsvej 122</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,20 +8861,20 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3404938</t>
+          <t xml:space="preserve">3402728</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H148">
-        <v>951</v>
+        <v>711</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043097</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8911,30 +8911,30 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbyvej 1</t>
+          <t xml:space="preserve">Solsikkevej 2A</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406264</t>
+          <t xml:space="preserve">1802218</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H149">
-        <v>777</v>
+        <v>1609</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043087</t>
+          <t xml:space="preserve">200043059</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8971,30 +8971,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prins Burisvej 2</t>
+          <t xml:space="preserve">Søndergade 36</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7770</t>
+          <t xml:space="preserve">7741</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3433444</t>
+          <t xml:space="preserve">9819885</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H150">
-        <v>4284</v>
+        <v>1610</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043075</t>
+          <t xml:space="preserve">200043064</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 18</t>
+          <t xml:space="preserve">Søndergade 36B</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7741</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569798</t>
+          <t xml:space="preserve">9819885</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,11 +9050,11 @@
         </is>
       </c>
       <c r="H151">
-        <v>1197</v>
+        <v>885</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043063</t>
+          <t xml:space="preserve">200043064</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -9091,30 +9091,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 36B</t>
+          <t xml:space="preserve">Vesterbyvej 1</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">7741</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9819885</t>
+          <t xml:space="preserve">3406264</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H152">
-        <v>885</v>
+        <v>777</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043064</t>
+          <t xml:space="preserve">200043087</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9151,35 +9151,35 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 36</t>
+          <t xml:space="preserve">Ydbyvej 45</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7741</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9819885</t>
+          <t xml:space="preserve">3424284</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H153">
-        <v>1610</v>
+        <v>624</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043064</t>
+          <t xml:space="preserve">200043148</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-16</t>
+          <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -9211,17 +9211,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydbyvej 45</t>
+          <t xml:space="preserve">Skolegade 2C</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3424284</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9230,16 +9230,16 @@
         </is>
       </c>
       <c r="H154">
-        <v>624</v>
+        <v>251</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043148</t>
+          <t xml:space="preserve">200045608</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-12-17</t>
+          <t xml:space="preserve">2021-02-14</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2C</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9286,20 +9286,20 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H155">
-        <v>251</v>
+        <v>787</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045608</t>
+          <t xml:space="preserve">200045929</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-14</t>
+          <t xml:space="preserve">2021-02-22</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Vesterbyvej 3</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9341,25 +9341,25 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">3406264</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H156">
-        <v>787</v>
+        <v>376</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">200045929</t>
+          <t xml:space="preserve">200046089</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-22</t>
+          <t xml:space="preserve">2021-02-24</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -9391,35 +9391,35 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbyvej 3</t>
+          <t xml:space="preserve">Fremvej 2</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3406264</t>
+          <t xml:space="preserve">7845330</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H157">
-        <v>376</v>
+        <v>1959</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046089</t>
+          <t xml:space="preserve">200046374</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-02-24</t>
+          <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørre Alle 21</t>
+          <t xml:space="preserve">Kirkevej 9</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">3425933</t>
+          <t xml:space="preserve">7845330</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9470,11 +9470,11 @@
         </is>
       </c>
       <c r="H158">
-        <v>4456</v>
+        <v>1199</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046380</t>
+          <t xml:space="preserve">200046374</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 9</t>
+          <t xml:space="preserve">Nørre Alle 21</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">7845330</t>
+          <t xml:space="preserve">3425933</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9530,11 +9530,11 @@
         </is>
       </c>
       <c r="H159">
-        <v>1199</v>
+        <v>4456</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046374</t>
+          <t xml:space="preserve">200046380</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9571,35 +9571,35 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fremvej 2</t>
+          <t xml:space="preserve">Skolegade 4A</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">7845330</t>
+          <t xml:space="preserve">5569579</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H160">
-        <v>1959</v>
+        <v>4295</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">200046374</t>
+          <t xml:space="preserve">200050161</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-03</t>
+          <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -9751,35 +9751,35 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 4A</t>
+          <t xml:space="preserve">Kløvervej 3</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569579</t>
+          <t xml:space="preserve">3418528</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H163">
-        <v>4295</v>
+        <v>2790</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050161</t>
+          <t xml:space="preserve">310000809</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-14</t>
+          <t xml:space="preserve">2022-06-28</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -9811,35 +9811,35 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervej 3</t>
+          <t xml:space="preserve">Jernbanegade 21</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3418528</t>
+          <t xml:space="preserve">3426087</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H164">
-        <v>2790</v>
+        <v>1944</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000809</t>
+          <t xml:space="preserve">310034756</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-28</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -9871,35 +9871,35 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 21</t>
+          <t xml:space="preserve">Solgårdsvej 14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3426087</t>
+          <t xml:space="preserve">3407563</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H165">
-        <v>1944</v>
+        <v>3813</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034756</t>
+          <t xml:space="preserve">311015451</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-12</t>
+          <t xml:space="preserve">2023-09-03</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -9931,35 +9931,35 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 14</t>
+          <t xml:space="preserve">Jernbanegade 19B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3407563</t>
+          <t xml:space="preserve">100054071</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H166">
-        <v>3813</v>
+        <v>1112</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311015451</t>
+          <t xml:space="preserve">311053110</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-09-03</t>
+          <t xml:space="preserve">2024-05-08</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -9991,35 +9991,35 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 19B</t>
+          <t xml:space="preserve">Grønningen 12A</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">100054071</t>
+          <t xml:space="preserve">8125673</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H167">
-        <v>1112</v>
+        <v>380</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053110</t>
+          <t xml:space="preserve">311074174</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-08</t>
+          <t xml:space="preserve">2024-09-18</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 12A</t>
+          <t xml:space="preserve">Vorupørvej 119</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10061,25 +10061,25 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8125673</t>
+          <t xml:space="preserve">3407465</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H168">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311074174</t>
+          <t xml:space="preserve">311098817</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-09-18</t>
+          <t xml:space="preserve">2025-03-04</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorupørvej 119</t>
+          <t xml:space="preserve">Brandbakken 4</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3407465</t>
+          <t xml:space="preserve">100071617</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -10130,16 +10130,16 @@
         </is>
       </c>
       <c r="H169">
-        <v>366</v>
+        <v>550</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098817</t>
+          <t xml:space="preserve">311155911</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-04</t>
+          <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -10171,17 +10171,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandbakken 4</t>
+          <t xml:space="preserve">Korsgade 18</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">100071617</t>
+          <t xml:space="preserve">7008753</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -10190,26 +10190,26 @@
         </is>
       </c>
       <c r="H170">
-        <v>550</v>
+        <v>1014</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311155911</t>
+          <t xml:space="preserve">311221399</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-28</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 18</t>
+          <t xml:space="preserve">Korsgade 20</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10246,15 +10246,15 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H171">
-        <v>1014</v>
+        <v>402</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221399</t>
+          <t xml:space="preserve">311221400</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsgade 20</t>
+          <t xml:space="preserve">Thorstedvej 21</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10301,25 +10301,25 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7008753</t>
+          <t xml:space="preserve">7683537</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H172">
-        <v>402</v>
+        <v>857</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221400</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -10366,11 +10366,11 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="H173">
-        <v>857</v>
+        <v>1434</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -10426,11 +10426,11 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H174">
-        <v>1434</v>
+        <v>1042</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -10486,11 +10486,11 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H175">
-        <v>1042</v>
+        <v>880</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -10546,11 +10546,11 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H176">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -10606,11 +10606,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H177">
-        <v>891</v>
+        <v>857</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstedvej 21</t>
+          <t xml:space="preserve">Kirkegårdsvej 11</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10661,25 +10661,25 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7683537</t>
+          <t xml:space="preserve">5569460</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H178">
-        <v>857</v>
+        <v>269</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311236522</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 11</t>
+          <t xml:space="preserve">Kronborgvej 28</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569460</t>
+          <t xml:space="preserve">8898152</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -10730,16 +10730,16 @@
         </is>
       </c>
       <c r="H179">
-        <v>269</v>
+        <v>418</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311236522</t>
+          <t xml:space="preserve">311241555</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-24</t>
+          <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -10786,15 +10786,15 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H180">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241555</t>
+          <t xml:space="preserve">311241554</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kronborgvej 28</t>
+          <t xml:space="preserve">Asylgade 22</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,25 +10841,25 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">8898152</t>
+          <t xml:space="preserve">5569465</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H181">
-        <v>424</v>
+        <v>607</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311241554</t>
+          <t xml:space="preserve">311244213</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-19</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 22</t>
+          <t xml:space="preserve">Silstrupvej 43</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,25 +10901,25 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5569465</t>
+          <t xml:space="preserve">3414578</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H182">
-        <v>607</v>
+        <v>433</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244213</t>
+          <t xml:space="preserve">311244324</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silstrupvej 43</t>
+          <t xml:space="preserve">Silstrupvej 45</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10966,11 +10966,11 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H183">
-        <v>433</v>
+        <v>280</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silstrupvej 45</t>
+          <t xml:space="preserve">Silstrupvej 47</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11026,11 +11026,11 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H184">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -11086,11 +11086,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H185">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -11146,11 +11146,11 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H186">
-        <v>377</v>
+        <v>2530</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silstrupvej 47</t>
+          <t xml:space="preserve">Tingstrupvej 13</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11201,25 +11201,25 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414578</t>
+          <t xml:space="preserve">5570156</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H187">
-        <v>2530</v>
+        <v>300</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311244324</t>
+          <t xml:space="preserve">311247496</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-01</t>
+          <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -11251,17 +11251,17 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstrupvej 13</t>
+          <t xml:space="preserve">Bytorvet 2</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570156</t>
+          <t xml:space="preserve">3396587</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -11270,16 +11270,16 @@
         </is>
       </c>
       <c r="H188">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247496</t>
+          <t xml:space="preserve">311247809</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-15</t>
+          <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -11311,17 +11311,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytorvet 2</t>
+          <t xml:space="preserve">Dragskilde 1</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3396587</t>
+          <t xml:space="preserve">7831930</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -11330,16 +11330,16 @@
         </is>
       </c>
       <c r="H189">
-        <v>255</v>
+        <v>460</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311247809</t>
+          <t xml:space="preserve">311248209</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-16</t>
+          <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragskilde 1</t>
+          <t xml:space="preserve">Dragskilde 5</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7831930</t>
+          <t xml:space="preserve">7831931</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -11390,11 +11390,11 @@
         </is>
       </c>
       <c r="H190">
-        <v>460</v>
+        <v>704</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248209</t>
+          <t xml:space="preserve">311248207</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dragskilde 5</t>
+          <t xml:space="preserve">Kastanievej 45</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11441,25 +11441,25 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7831931</t>
+          <t xml:space="preserve">8113565</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H191">
-        <v>704</v>
+        <v>340</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311248207</t>
+          <t xml:space="preserve">311249314</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-18</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 45</t>
+          <t xml:space="preserve">Skyumvej 53</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11561,25 +11561,25 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">8113565</t>
+          <t xml:space="preserve">3413076</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H193">
-        <v>340</v>
+        <v>405</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249314</t>
+          <t xml:space="preserve">311250207</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -11611,35 +11611,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skyumvej 53</t>
+          <t xml:space="preserve">Glaspustervej 2</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413076</t>
+          <t xml:space="preserve">3397380</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H194">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250207</t>
+          <t xml:space="preserve">311250316</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -11671,17 +11671,17 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glaspustervej 2</t>
+          <t xml:space="preserve">Vorupørvej 147</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3397380</t>
+          <t xml:space="preserve">3407838</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -11690,11 +11690,11 @@
         </is>
       </c>
       <c r="H195">
-        <v>434</v>
+        <v>286</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250316</t>
+          <t xml:space="preserve">311250468</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11731,17 +11731,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorupørvej 147</t>
+          <t xml:space="preserve">Hjulmagervej 3</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3407838</t>
+          <t xml:space="preserve">3397466</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -11750,16 +11750,16 @@
         </is>
       </c>
       <c r="H196">
-        <v>286</v>
+        <v>435</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250468</t>
+          <t xml:space="preserve">311251041</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -11791,17 +11791,17 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjulmagervej 3</t>
+          <t xml:space="preserve">Tigervej 6</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3397466</t>
+          <t xml:space="preserve">5574741</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -11810,11 +11810,11 @@
         </is>
       </c>
       <c r="H197">
-        <v>435</v>
+        <v>500</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251041</t>
+          <t xml:space="preserve">311251069</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tigervej 6</t>
+          <t xml:space="preserve">Kirsebærvænget 2</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7752</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5574741</t>
+          <t xml:space="preserve">3419315</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251072</t>
+          <t xml:space="preserve">311251314</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -11911,30 +11911,30 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftholmvej 17</t>
+          <t xml:space="preserve">Kløvermarken 2</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7760</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3405225</t>
+          <t xml:space="preserve">3427190</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H199">
-        <v>308</v>
+        <v>483</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251269</t>
+          <t xml:space="preserve">311251404</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11971,30 +11971,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærvænget 2</t>
+          <t xml:space="preserve">Toftholmvej 17</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7752</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3419315</t>
+          <t xml:space="preserve">3405225</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H200">
-        <v>500</v>
+        <v>308</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251314</t>
+          <t xml:space="preserve">311251269</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12031,17 +12031,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvermarken 2</t>
+          <t xml:space="preserve">Østerbakken 95</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7760</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3427190</t>
+          <t xml:space="preserve">9509437</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -12050,16 +12050,16 @@
         </is>
       </c>
       <c r="H201">
-        <v>483</v>
+        <v>518</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251404</t>
+          <t xml:space="preserve">311254748</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -12091,35 +12091,35 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbakken 95</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">7700</t>
+          <t xml:space="preserve">7741</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">9509437</t>
+          <t xml:space="preserve">7969712</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H202">
-        <v>518</v>
+        <v>479</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254748</t>
+          <t xml:space="preserve">311263644</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-07-30</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -12151,35 +12151,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Fyrvej 100</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7741</t>
+          <t xml:space="preserve">7730</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969712</t>
+          <t xml:space="preserve">3396693</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H203">
-        <v>479</v>
+        <v>4009</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263644</t>
+          <t xml:space="preserve">311263898</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-30</t>
+          <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -12226,11 +12226,11 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H204">
-        <v>4009</v>
+        <v>758</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -12286,11 +12286,11 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H205">
-        <v>758</v>
+        <v>1850</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -12346,11 +12346,11 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H206">
-        <v>1850</v>
+        <v>1242</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -12391,30 +12391,30 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvej 100</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7730</t>
+          <t xml:space="preserve">7741</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3396693</t>
+          <t xml:space="preserve">7969712</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H207">
-        <v>1242</v>
+        <v>1440</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263898</t>
+          <t xml:space="preserve">311263895</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12466,11 +12466,11 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H208">
-        <v>1440</v>
+        <v>691</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Skolevej 3</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12526,11 +12526,11 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H209">
-        <v>691</v>
+        <v>738</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -12571,35 +12571,35 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 3</t>
+          <t xml:space="preserve">Tingstrupvej 17</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7741</t>
+          <t xml:space="preserve">7700</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">7969712</t>
+          <t xml:space="preserve">5570155</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H210">
-        <v>738</v>
+        <v>1260</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311263895</t>
+          <t xml:space="preserve">311346981</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-01</t>
+          <t xml:space="preserve">2028-11-15</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingstrupvej 17</t>
+          <t xml:space="preserve">Håndværker Torv 1</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12641,25 +12641,25 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5570155</t>
+          <t xml:space="preserve">378951, 378952, 378953, 378954, 378955</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H211">
-        <v>1260</v>
+        <v>3405</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346981</t>
+          <t xml:space="preserve">311361096</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-15</t>
+          <t xml:space="preserve">2029-02-22</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">

--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -8814,7 +8814,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">

--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -8754,7 +8754,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043071</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251069</t>
+          <t xml:space="preserve">311251072</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">

--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L226"/>
+  <dimension ref="A1:M226"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2464,10 +2664,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2524,10 +2729,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2584,10 +2794,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2644,10 +2859,15 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2704,10 +2924,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2764,10 +2989,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2824,10 +3054,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2884,10 +3119,15 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2944,10 +3184,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3004,10 +3249,15 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3064,10 +3314,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3124,10 +3379,15 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3184,10 +3444,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3244,10 +3509,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3304,10 +3574,15 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3364,10 +3639,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3424,10 +3704,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3484,10 +3769,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3544,10 +3834,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3604,10 +3899,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3664,10 +3964,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3724,10 +4029,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3784,10 +4094,15 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3844,10 +4159,15 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3904,10 +4224,15 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3964,10 +4289,15 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4024,10 +4354,15 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4084,10 +4419,15 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4144,10 +4484,15 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4204,10 +4549,15 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4264,10 +4614,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4324,10 +4679,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4384,10 +4744,15 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4444,10 +4809,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4504,10 +4874,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4564,10 +4939,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4624,10 +5004,15 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4684,10 +5069,15 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4744,10 +5134,15 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4804,10 +5199,15 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4864,10 +5264,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4924,10 +5329,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4984,10 +5394,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5044,10 +5459,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5104,10 +5524,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5164,10 +5589,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5224,10 +5654,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5284,10 +5719,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5344,10 +5784,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5404,10 +5849,15 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5464,10 +5914,15 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5524,10 +5979,15 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5584,10 +6044,15 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-26</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-19</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-07-31</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-09-18</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-10-12</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-11-26</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-07</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-01-08</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-12</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-02-22</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-03</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">Thaning Miljø- og Energirådgivning F.R.I</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-11</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-03-15</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-07-15</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-19</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-08-19</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-09-28</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-08</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-19</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-11-30</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-08</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-13</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-15</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-15</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8754,20 +9479,25 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8814,20 +9544,25 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8874,20 +9609,25 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-16</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-12-17</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-14</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-22</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-02-24</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-03</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-14</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-06-28</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-09-03</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vh-consult</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-05-08</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-09-18</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Thisted</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-03-04</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-28</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Orbicon A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10314,20 +11169,25 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10374,20 +11234,25 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10434,20 +11299,25 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10494,20 +11364,25 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10554,20 +11429,25 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10614,20 +11494,25 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-24</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-19</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-01</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-15</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-16</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-18</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-07-30</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-08-01</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">A.N. Arkitekter</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2028-11-15</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-22</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-03-17</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">Scanenergi A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-04</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-03-25</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-03</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-02-16</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Factum2 A/S</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-23</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiConsult ApS</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">HJ-Energi ApS</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-07-03</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Xpertråd aps</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-24</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Xpertråd aps</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-03-24</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,21 +14684,26 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L226"/>
+  <autoFilter ref="A1:M226"/>
 </worksheet>
 </file>
--- a/public/exports/29189560.xlsx
+++ b/public/exports/29189560.xlsx
@@ -7464,7 +7464,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027989</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251072</t>
+          <t xml:space="preserve">311251069</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
